--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ141"/>
+  <dimension ref="A1:AZ142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4995,58 +4995,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123563043</v>
+        <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58636</v>
+        <v>58169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524035</v>
+        <v>524075</v>
       </c>
       <c r="R38" t="n">
-        <v>6713295</v>
+        <v>6713944</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5070,22 +5065,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5111,13 +5106,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123563043</t>
+          <t>https://artportalen.se/Sighting/136991757</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123568031</v>
+        <v>123563043</v>
       </c>
       <c r="B39" t="n">
         <v>58636</v>
@@ -5146,6 +5141,11 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -5157,13 +5157,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524094</v>
+        <v>524035</v>
       </c>
       <c r="R39" t="n">
-        <v>6713439</v>
+        <v>6713295</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5228,16 +5228,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123568031</t>
+          <t>https://artportalen.se/Sighting/123563043</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122915863</v>
+        <v>123568031</v>
       </c>
       <c r="B40" t="n">
-        <v>8455</v>
+        <v>58636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5245,39 +5245,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>103044</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524025</v>
+        <v>524094</v>
       </c>
       <c r="R40" t="n">
-        <v>6713544</v>
+        <v>6713439</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5304,22 +5304,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5345,13 +5345,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122915863</t>
+          <t>https://artportalen.se/Sighting/123568031</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122959354</v>
+        <v>122915863</v>
       </c>
       <c r="B41" t="n">
         <v>8455</v>
@@ -5387,14 +5387,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524122</v>
+        <v>524025</v>
       </c>
       <c r="R41" t="n">
-        <v>6713710</v>
+        <v>6713544</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5421,22 +5421,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5462,13 +5462,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122959354</t>
+          <t>https://artportalen.se/Sighting/122915863</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122959453</v>
+        <v>122959354</v>
       </c>
       <c r="B42" t="n">
         <v>8455</v>
@@ -5508,10 +5508,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524128</v>
+        <v>524122</v>
       </c>
       <c r="R42" t="n">
-        <v>6713669</v>
+        <v>6713710</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5579,13 +5579,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122959453</t>
+          <t>https://artportalen.se/Sighting/122959354</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123761045</v>
+        <v>122959453</v>
       </c>
       <c r="B43" t="n">
         <v>8455</v>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523984</v>
+        <v>524128</v>
       </c>
       <c r="R43" t="n">
-        <v>6713796</v>
+        <v>6713669</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5655,22 +5655,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5696,13 +5696,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123761045</t>
+          <t>https://artportalen.se/Sighting/122959453</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124434324</v>
+        <v>123761045</v>
       </c>
       <c r="B44" t="n">
         <v>8455</v>
@@ -5738,14 +5738,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524045</v>
+        <v>523984</v>
       </c>
       <c r="R44" t="n">
-        <v>6713403</v>
+        <v>6713796</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5772,22 +5772,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5813,68 +5813,59 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124434324</t>
+          <t>https://artportalen.se/Sighting/123761045</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118680065</v>
+        <v>124434324</v>
       </c>
       <c r="B45" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524085</v>
+        <v>524045</v>
       </c>
       <c r="R45" t="n">
-        <v>6714124</v>
+        <v>6713403</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5898,27 +5889,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Under mindre gran intill större tall, i blom och minst 20 rosetter.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5944,13 +5930,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680065</t>
+          <t>https://artportalen.se/Sighting/124434324</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118680241</v>
+        <v>118680065</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5980,7 +5966,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5988,11 +5974,6 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6004,10 +5985,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524096</v>
+        <v>524085</v>
       </c>
       <c r="R46" t="n">
-        <v>6714118</v>
+        <v>6714124</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -6039,7 +6020,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6049,12 +6030,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Några i blom.</t>
+          <t>Under mindre gran intill större tall, i blom och minst 20 rosetter.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6080,13 +6061,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680241</t>
+          <t>https://artportalen.se/Sighting/118680065</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118680271</v>
+        <v>118680241</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -6116,12 +6097,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6140,10 +6121,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524098</v>
+        <v>524096</v>
       </c>
       <c r="R47" t="n">
-        <v>6714108</v>
+        <v>6714118</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -6190,7 +6171,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ca 10 rosetter några i blom</t>
+          <t>Några i blom.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6216,13 +6197,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680271</t>
+          <t>https://artportalen.se/Sighting/118680241</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118680340</v>
+        <v>118680271</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -6257,7 +6238,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6276,10 +6257,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524081</v>
+        <v>524098</v>
       </c>
       <c r="R48" t="n">
-        <v>6714116</v>
+        <v>6714108</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -6311,7 +6292,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6321,12 +6302,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Mycket i blom och rosetter.</t>
+          <t>Ca 10 rosetter några i blom</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6352,13 +6333,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680340</t>
+          <t>https://artportalen.se/Sighting/118680271</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118680431</v>
+        <v>118680340</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -6388,12 +6369,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6412,10 +6393,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524105</v>
+        <v>524081</v>
       </c>
       <c r="R49" t="n">
-        <v>6714054</v>
+        <v>6714116</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -6447,7 +6428,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6457,7 +6438,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Mycket i blom och rosetter.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6483,13 +6469,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680431</t>
+          <t>https://artportalen.se/Sighting/118680340</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118680590</v>
+        <v>118680431</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -6519,7 +6505,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6543,10 +6529,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524083</v>
+        <v>524105</v>
       </c>
       <c r="R50" t="n">
-        <v>6714083</v>
+        <v>6714054</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6578,7 +6564,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6588,7 +6574,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6614,13 +6600,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680590</t>
+          <t>https://artportalen.se/Sighting/118680431</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118680966</v>
+        <v>118680590</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -6650,12 +6636,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -6674,10 +6660,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524064</v>
+        <v>524083</v>
       </c>
       <c r="R51" t="n">
-        <v>6714092</v>
+        <v>6714083</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6709,7 +6695,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6719,12 +6705,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>I blom och fler rosetter på fler fläckar.</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6750,13 +6731,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680966</t>
+          <t>https://artportalen.se/Sighting/118680590</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122817980</v>
+        <v>118680966</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6791,12 +6772,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6806,17 +6787,17 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524038</v>
+        <v>524064</v>
       </c>
       <c r="R52" t="n">
-        <v>6713288</v>
+        <v>6714092</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6840,27 +6821,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>I blom och fler rosetter på fler fläckar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6886,13 +6867,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122817980</t>
+          <t>https://artportalen.se/Sighting/118680966</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122821104</v>
+        <v>122817980</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6922,12 +6903,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -6942,14 +6923,14 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524057</v>
+        <v>524038</v>
       </c>
       <c r="R53" t="n">
-        <v>6714094</v>
+        <v>6713288</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6981,7 +6962,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6991,12 +6972,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7022,13 +7003,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122821104</t>
+          <t>https://artportalen.se/Sighting/122817980</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122821198</v>
+        <v>122821104</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -7058,12 +7039,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -7071,7 +7052,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7083,10 +7063,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524049</v>
+        <v>524057</v>
       </c>
       <c r="R54" t="n">
-        <v>6714097</v>
+        <v>6714094</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7098,7 +7078,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -7133,7 +7113,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7142,7 +7122,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7160,13 +7139,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122821198</t>
+          <t>https://artportalen.se/Sighting/122821104</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122821729</v>
+        <v>122821198</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -7196,12 +7175,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7209,6 +7188,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7220,10 +7200,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524077</v>
+        <v>524049</v>
       </c>
       <c r="R55" t="n">
-        <v>6714076</v>
+        <v>6714097</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7235,7 +7215,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -7255,7 +7235,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7265,12 +7245,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7279,6 +7259,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7296,13 +7277,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122821729</t>
+          <t>https://artportalen.se/Sighting/122821198</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122821745</v>
+        <v>122821729</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -7332,7 +7313,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7356,10 +7337,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524080</v>
+        <v>524077</v>
       </c>
       <c r="R56" t="n">
-        <v>6714074</v>
+        <v>6714076</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7391,7 +7372,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7401,7 +7382,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7427,13 +7413,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122821745</t>
+          <t>https://artportalen.se/Sighting/122821729</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122821824</v>
+        <v>122821745</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -7468,7 +7454,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7487,10 +7473,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524055</v>
+        <v>524080</v>
       </c>
       <c r="R57" t="n">
-        <v>6714048</v>
+        <v>6714074</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7522,7 +7508,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7532,7 +7518,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7558,13 +7544,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122821824</t>
+          <t>https://artportalen.se/Sighting/122821745</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122916997</v>
+        <v>122821824</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -7594,12 +7580,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7614,14 +7600,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524142</v>
+        <v>524055</v>
       </c>
       <c r="R58" t="n">
-        <v>6713729</v>
+        <v>6714048</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7648,27 +7634,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7694,13 +7675,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122916997</t>
+          <t>https://artportalen.se/Sighting/122821824</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122917069</v>
+        <v>122916997</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -7730,12 +7711,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7754,7 +7735,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524154</v>
+        <v>524142</v>
       </c>
       <c r="R59" t="n">
         <v>6713729</v>
@@ -7789,7 +7770,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7799,12 +7780,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7830,13 +7811,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122917069</t>
+          <t>https://artportalen.se/Sighting/122916997</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122957710</v>
+        <v>122917069</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -7866,7 +7847,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7879,16 +7860,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524145</v>
+        <v>524154</v>
       </c>
       <c r="R60" t="n">
-        <v>6713733</v>
+        <v>6713729</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7915,27 +7901,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Under klena granar.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7961,13 +7947,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122957710</t>
+          <t>https://artportalen.se/Sighting/122917069</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122958064</v>
+        <v>122957710</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -7997,12 +7983,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -8010,21 +7996,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524144</v>
+        <v>524145</v>
       </c>
       <c r="R61" t="n">
-        <v>6713722</v>
+        <v>6713733</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8056,7 +8037,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8066,12 +8047,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8097,13 +8078,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958064</t>
+          <t>https://artportalen.se/Sighting/122957710</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122958244</v>
+        <v>122958064</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -8133,12 +8114,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -8157,10 +8138,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524143</v>
+        <v>524144</v>
       </c>
       <c r="R62" t="n">
-        <v>6713721</v>
+        <v>6713722</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8192,7 +8173,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8202,12 +8183,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8233,13 +8214,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958244</t>
+          <t>https://artportalen.se/Sighting/122958064</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122958484</v>
+        <v>122958244</v>
       </c>
       <c r="B63" t="n">
         <v>99118</v>
@@ -8269,7 +8250,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8293,10 +8274,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524142</v>
+        <v>524143</v>
       </c>
       <c r="R63" t="n">
-        <v>6713723</v>
+        <v>6713721</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8328,7 +8309,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8338,7 +8319,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8364,13 +8350,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958484</t>
+          <t>https://artportalen.se/Sighting/122958244</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122958550</v>
+        <v>122958484</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -8400,7 +8386,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8424,10 +8410,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524147</v>
+        <v>524142</v>
       </c>
       <c r="R64" t="n">
-        <v>6713728</v>
+        <v>6713723</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8459,7 +8445,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8469,12 +8455,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8500,13 +8481,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958550</t>
+          <t>https://artportalen.se/Sighting/122958484</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122958631</v>
+        <v>122958550</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -8536,7 +8517,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8560,10 +8541,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524136</v>
+        <v>524147</v>
       </c>
       <c r="R65" t="n">
-        <v>6713723</v>
+        <v>6713728</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8595,7 +8576,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8605,12 +8586,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8636,13 +8617,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958631</t>
+          <t>https://artportalen.se/Sighting/122958550</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122959503</v>
+        <v>122958631</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -8672,12 +8653,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8685,16 +8666,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524145</v>
+        <v>524136</v>
       </c>
       <c r="R66" t="n">
-        <v>6713672</v>
+        <v>6713723</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8726,7 +8712,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8736,7 +8722,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8762,13 +8753,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122959503</t>
+          <t>https://artportalen.se/Sighting/122958631</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123412257</v>
+        <v>122959503</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -8798,7 +8789,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8813,14 +8804,14 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524123</v>
+        <v>524145</v>
       </c>
       <c r="R67" t="n">
-        <v>6713637</v>
+        <v>6713672</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8847,22 +8838,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8888,13 +8879,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123412257</t>
+          <t>https://artportalen.se/Sighting/122959503</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123412326</v>
+        <v>123412257</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -8924,7 +8915,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8943,10 +8934,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524122</v>
+        <v>524123</v>
       </c>
       <c r="R68" t="n">
-        <v>6713640</v>
+        <v>6713637</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8978,7 +8969,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8988,7 +8979,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9014,13 +9005,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123412326</t>
+          <t>https://artportalen.se/Sighting/123412257</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123412367</v>
+        <v>123412326</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -9050,7 +9041,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9065,14 +9056,14 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524136</v>
+        <v>524122</v>
       </c>
       <c r="R69" t="n">
-        <v>6713648</v>
+        <v>6713640</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9104,7 +9095,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9114,7 +9105,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9140,13 +9131,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123412367</t>
+          <t>https://artportalen.se/Sighting/123412326</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123412439</v>
+        <v>123412367</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -9176,7 +9167,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9189,21 +9180,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524137</v>
+        <v>524136</v>
       </c>
       <c r="R70" t="n">
-        <v>6713646</v>
+        <v>6713648</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9235,7 +9221,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9245,12 +9231,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9276,13 +9257,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123412439</t>
+          <t>https://artportalen.se/Sighting/123412367</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123412973</v>
+        <v>123412439</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -9312,7 +9293,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9336,10 +9317,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>524116</v>
+        <v>524137</v>
       </c>
       <c r="R71" t="n">
-        <v>6713634</v>
+        <v>6713646</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9371,7 +9352,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9381,7 +9362,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9407,13 +9393,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123412973</t>
+          <t>https://artportalen.se/Sighting/123412439</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123413078</v>
+        <v>123412973</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -9443,7 +9429,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9463,14 +9449,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524102</v>
+        <v>524116</v>
       </c>
       <c r="R72" t="n">
-        <v>6713632</v>
+        <v>6713634</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9502,7 +9488,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9512,7 +9498,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9538,13 +9524,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123413078</t>
+          <t>https://artportalen.se/Sighting/123412973</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123413119</v>
+        <v>123413078</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -9574,12 +9560,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -9587,7 +9573,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9599,10 +9584,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524101</v>
+        <v>524102</v>
       </c>
       <c r="R73" t="n">
-        <v>6713638</v>
+        <v>6713632</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9634,7 +9619,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9644,12 +9629,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9658,7 +9638,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9676,13 +9655,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123413119</t>
+          <t>https://artportalen.se/Sighting/123413078</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123413726</v>
+        <v>123413119</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -9717,7 +9696,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -9725,16 +9704,22 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524030</v>
+        <v>524101</v>
       </c>
       <c r="R74" t="n">
-        <v>6713469</v>
+        <v>6713638</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9766,7 +9751,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9776,7 +9761,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9785,6 +9775,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9802,13 +9793,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123413726</t>
+          <t>https://artportalen.se/Sighting/123413119</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123413856</v>
+        <v>123413726</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -9838,7 +9829,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9857,10 +9848,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524041</v>
+        <v>524030</v>
       </c>
       <c r="R75" t="n">
-        <v>6713443</v>
+        <v>6713469</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9892,7 +9883,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9902,7 +9893,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9928,13 +9919,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123413856</t>
+          <t>https://artportalen.se/Sighting/123413726</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123414270</v>
+        <v>123413856</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -9964,7 +9955,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9983,10 +9974,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524085</v>
+        <v>524041</v>
       </c>
       <c r="R76" t="n">
-        <v>6713390</v>
+        <v>6713443</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10018,7 +10009,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10028,7 +10019,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10054,13 +10045,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123414270</t>
+          <t>https://artportalen.se/Sighting/123413856</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123414352</v>
+        <v>123414270</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -10090,7 +10081,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10109,10 +10100,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524098</v>
+        <v>524085</v>
       </c>
       <c r="R77" t="n">
-        <v>6713405</v>
+        <v>6713390</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10144,7 +10135,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10154,7 +10145,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10180,13 +10171,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123414352</t>
+          <t>https://artportalen.se/Sighting/123414270</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123525488</v>
+        <v>123414352</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -10221,7 +10212,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -10229,21 +10220,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524128</v>
+        <v>524098</v>
       </c>
       <c r="R78" t="n">
-        <v>6714020</v>
+        <v>6713405</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10270,27 +10256,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10316,13 +10297,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123525488</t>
+          <t>https://artportalen.se/Sighting/123414352</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123526406</v>
+        <v>123525488</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -10352,7 +10333,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10376,10 +10357,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524109</v>
+        <v>524128</v>
       </c>
       <c r="R79" t="n">
-        <v>6713892</v>
+        <v>6714020</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10411,7 +10392,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10421,12 +10402,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10452,13 +10433,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123526406</t>
+          <t>https://artportalen.se/Sighting/123525488</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123526470</v>
+        <v>123526406</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -10488,12 +10469,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -10512,10 +10493,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524101</v>
+        <v>524109</v>
       </c>
       <c r="R80" t="n">
-        <v>6713880</v>
+        <v>6713892</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10547,7 +10528,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10557,7 +10538,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10583,13 +10569,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123526470</t>
+          <t>https://artportalen.se/Sighting/123526406</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123527655</v>
+        <v>123526470</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -10619,7 +10605,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10632,16 +10618,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524041</v>
+        <v>524101</v>
       </c>
       <c r="R81" t="n">
-        <v>6713460</v>
+        <v>6713880</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10673,7 +10664,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10683,7 +10674,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10709,13 +10700,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123527655</t>
+          <t>https://artportalen.se/Sighting/123526470</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123527741</v>
+        <v>123527655</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -10745,12 +10736,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -10758,18 +10749,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524029</v>
+        <v>524041</v>
       </c>
       <c r="R82" t="n">
-        <v>6713459</v>
+        <v>6713460</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10801,7 +10790,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10811,12 +10800,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10825,7 +10809,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -10843,13 +10826,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123527741</t>
+          <t>https://artportalen.se/Sighting/123527655</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123528345</v>
+        <v>123527741</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -10879,7 +10862,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10900,10 +10883,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524025</v>
+        <v>524029</v>
       </c>
       <c r="R83" t="n">
-        <v>6713476</v>
+        <v>6713459</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10935,7 +10918,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10945,12 +10928,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10977,13 +10960,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123528345</t>
+          <t>https://artportalen.se/Sighting/123527741</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123564666</v>
+        <v>123528345</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -11013,12 +10996,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -11026,16 +11009,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524034</v>
+        <v>524025</v>
       </c>
       <c r="R84" t="n">
-        <v>6713303</v>
+        <v>6713476</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11062,22 +11047,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11086,6 +11076,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -11103,13 +11094,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123564666</t>
+          <t>https://artportalen.se/Sighting/123528345</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123564906</v>
+        <v>123564666</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -11139,7 +11130,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11158,10 +11149,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524050</v>
+        <v>524034</v>
       </c>
       <c r="R85" t="n">
-        <v>6713310</v>
+        <v>6713303</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11193,7 +11184,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11203,7 +11194,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11229,13 +11220,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123564906</t>
+          <t>https://artportalen.se/Sighting/123564666</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123566656</v>
+        <v>123564906</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -11265,7 +11256,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11284,10 +11275,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524082</v>
+        <v>524050</v>
       </c>
       <c r="R86" t="n">
-        <v>6713393</v>
+        <v>6713310</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11319,7 +11310,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11329,7 +11320,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11355,13 +11346,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123566656</t>
+          <t>https://artportalen.se/Sighting/123564906</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123566767</v>
+        <v>123566656</v>
       </c>
       <c r="B87" t="n">
         <v>99118</v>
@@ -11391,7 +11382,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11410,10 +11401,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524084</v>
+        <v>524082</v>
       </c>
       <c r="R87" t="n">
-        <v>6713408</v>
+        <v>6713393</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11445,7 +11436,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11455,7 +11446,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11481,13 +11472,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123566767</t>
+          <t>https://artportalen.se/Sighting/123566656</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123567299</v>
+        <v>123566767</v>
       </c>
       <c r="B88" t="n">
         <v>99118</v>
@@ -11517,7 +11508,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11536,10 +11527,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524117</v>
+        <v>524084</v>
       </c>
       <c r="R88" t="n">
-        <v>6713411</v>
+        <v>6713408</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11571,7 +11562,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11581,7 +11572,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11607,13 +11598,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123567299</t>
+          <t>https://artportalen.se/Sighting/123566767</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123567823</v>
+        <v>123567299</v>
       </c>
       <c r="B89" t="n">
         <v>99118</v>
@@ -11643,7 +11634,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11662,10 +11653,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524093</v>
+        <v>524117</v>
       </c>
       <c r="R89" t="n">
-        <v>6713439</v>
+        <v>6713411</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11697,7 +11688,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11707,7 +11698,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11733,13 +11724,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123567823</t>
+          <t>https://artportalen.se/Sighting/123567299</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123570699</v>
+        <v>123567823</v>
       </c>
       <c r="B90" t="n">
         <v>99118</v>
@@ -11769,7 +11760,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11788,10 +11779,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>524145</v>
+        <v>524093</v>
       </c>
       <c r="R90" t="n">
-        <v>6713399</v>
+        <v>6713439</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11823,7 +11814,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11833,7 +11824,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11859,13 +11850,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123570699</t>
+          <t>https://artportalen.se/Sighting/123567823</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123760786</v>
+        <v>123570699</v>
       </c>
       <c r="B91" t="n">
         <v>99118</v>
@@ -11895,7 +11886,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11910,14 +11901,14 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523969</v>
+        <v>524145</v>
       </c>
       <c r="R91" t="n">
-        <v>6713750</v>
+        <v>6713399</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11944,22 +11935,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11985,13 +11976,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123760786</t>
+          <t>https://artportalen.se/Sighting/123570699</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123761091</v>
+        <v>123760786</v>
       </c>
       <c r="B92" t="n">
         <v>99118</v>
@@ -12021,7 +12012,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -12040,10 +12031,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523962</v>
+        <v>523969</v>
       </c>
       <c r="R92" t="n">
-        <v>6713819</v>
+        <v>6713750</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12075,7 +12066,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12085,7 +12076,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12111,13 +12102,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123761091</t>
+          <t>https://artportalen.se/Sighting/123760786</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124431501</v>
+        <v>123761091</v>
       </c>
       <c r="B93" t="n">
         <v>99118</v>
@@ -12147,7 +12138,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -12162,14 +12153,14 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>524175</v>
+        <v>523962</v>
       </c>
       <c r="R93" t="n">
-        <v>6713573</v>
+        <v>6713819</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12196,27 +12187,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12242,13 +12228,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124431501</t>
+          <t>https://artportalen.se/Sighting/123761091</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124431841</v>
+        <v>124431501</v>
       </c>
       <c r="B94" t="n">
         <v>99118</v>
@@ -12278,7 +12264,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -12297,10 +12283,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>524168</v>
+        <v>524175</v>
       </c>
       <c r="R94" t="n">
-        <v>6713526</v>
+        <v>6713573</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12332,7 +12318,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -12342,7 +12328,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12368,13 +12359,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124431841</t>
+          <t>https://artportalen.se/Sighting/124431501</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124432135</v>
+        <v>124431841</v>
       </c>
       <c r="B95" t="n">
         <v>99118</v>
@@ -12404,7 +12395,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -12423,10 +12414,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>524180</v>
+        <v>524168</v>
       </c>
       <c r="R95" t="n">
-        <v>6713485</v>
+        <v>6713526</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12458,7 +12449,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12468,7 +12459,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12494,13 +12485,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124432135</t>
+          <t>https://artportalen.se/Sighting/124431841</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124432412</v>
+        <v>124432135</v>
       </c>
       <c r="B96" t="n">
         <v>99118</v>
@@ -12530,7 +12521,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -12549,10 +12540,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524183</v>
+        <v>524180</v>
       </c>
       <c r="R96" t="n">
-        <v>6713449</v>
+        <v>6713485</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12584,7 +12575,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12594,7 +12585,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12620,13 +12611,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124432412</t>
+          <t>https://artportalen.se/Sighting/124432135</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124433963</v>
+        <v>124432412</v>
       </c>
       <c r="B97" t="n">
         <v>99118</v>
@@ -12656,7 +12647,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12675,10 +12666,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>524033</v>
+        <v>524183</v>
       </c>
       <c r="R97" t="n">
-        <v>6713451</v>
+        <v>6713449</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12710,7 +12701,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12720,7 +12711,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12746,13 +12737,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124433963</t>
+          <t>https://artportalen.se/Sighting/124432412</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124434100</v>
+        <v>124433963</v>
       </c>
       <c r="B98" t="n">
         <v>99118</v>
@@ -12782,7 +12773,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12795,21 +12786,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>524042</v>
+        <v>524033</v>
       </c>
       <c r="R98" t="n">
-        <v>6713423</v>
+        <v>6713451</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12841,7 +12827,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12851,12 +12837,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12882,13 +12863,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124434100</t>
+          <t>https://artportalen.se/Sighting/124433963</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124435133</v>
+        <v>124434100</v>
       </c>
       <c r="B99" t="n">
         <v>99118</v>
@@ -12918,7 +12899,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12938,14 +12919,14 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523934</v>
+        <v>524042</v>
       </c>
       <c r="R99" t="n">
-        <v>6713790</v>
+        <v>6713423</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12977,7 +12958,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12987,12 +12968,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>En vinterståndare.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13018,13 +12999,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124435133</t>
+          <t>https://artportalen.se/Sighting/124434100</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124711417</v>
+        <v>124435133</v>
       </c>
       <c r="B100" t="n">
         <v>99118</v>
@@ -13054,7 +13035,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -13067,16 +13048,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>524045</v>
+        <v>523934</v>
       </c>
       <c r="R100" t="n">
-        <v>6713421</v>
+        <v>6713790</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13103,22 +13089,27 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13144,13 +13135,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124711417</t>
+          <t>https://artportalen.se/Sighting/124435133</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125899247</v>
+        <v>124711417</v>
       </c>
       <c r="B101" t="n">
         <v>99118</v>
@@ -13180,7 +13171,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -13199,10 +13190,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>524042</v>
+        <v>524045</v>
       </c>
       <c r="R101" t="n">
-        <v>6713304</v>
+        <v>6713421</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13229,22 +13220,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13270,13 +13261,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125899247</t>
+          <t>https://artportalen.se/Sighting/124711417</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126932450</v>
+        <v>125899247</v>
       </c>
       <c r="B102" t="n">
         <v>99118</v>
@@ -13306,29 +13297,29 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>524097</v>
+        <v>524042</v>
       </c>
       <c r="R102" t="n">
-        <v>6713893</v>
+        <v>6713304</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13355,22 +13346,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13396,13 +13387,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932450</t>
+          <t>https://artportalen.se/Sighting/125899247</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126932846</v>
+        <v>126932450</v>
       </c>
       <c r="B103" t="n">
         <v>99118</v>
@@ -13432,7 +13423,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -13447,14 +13438,14 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>524149</v>
+        <v>524097</v>
       </c>
       <c r="R103" t="n">
-        <v>6713719</v>
+        <v>6713893</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13486,7 +13477,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13496,7 +13487,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13522,13 +13513,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932846</t>
+          <t>https://artportalen.se/Sighting/126932450</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126933275</v>
+        <v>126932846</v>
       </c>
       <c r="B104" t="n">
         <v>99118</v>
@@ -13558,7 +13549,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -13573,14 +13564,14 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>524034</v>
+        <v>524149</v>
       </c>
       <c r="R104" t="n">
-        <v>6713423</v>
+        <v>6713719</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13612,7 +13603,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13622,7 +13613,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13648,13 +13639,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126933275</t>
+          <t>https://artportalen.se/Sighting/126932846</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126933326</v>
+        <v>126933275</v>
       </c>
       <c r="B105" t="n">
         <v>99118</v>
@@ -13703,10 +13694,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>524053</v>
+        <v>524034</v>
       </c>
       <c r="R105" t="n">
-        <v>6713414</v>
+        <v>6713423</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13738,7 +13729,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13748,7 +13739,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13774,13 +13765,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126933326</t>
+          <t>https://artportalen.se/Sighting/126933275</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126933611</v>
+        <v>126933326</v>
       </c>
       <c r="B106" t="n">
         <v>99118</v>
@@ -13829,10 +13820,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>524037</v>
+        <v>524053</v>
       </c>
       <c r="R106" t="n">
-        <v>6713298</v>
+        <v>6713414</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13864,7 +13855,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13874,7 +13865,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13900,13 +13891,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126933611</t>
+          <t>https://artportalen.se/Sighting/126933326</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126933692</v>
+        <v>126933611</v>
       </c>
       <c r="B107" t="n">
         <v>99118</v>
@@ -13955,10 +13946,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>524033</v>
+        <v>524037</v>
       </c>
       <c r="R107" t="n">
-        <v>6713299</v>
+        <v>6713298</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14026,13 +14017,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126933692</t>
+          <t>https://artportalen.se/Sighting/126933611</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126934164</v>
+        <v>126933692</v>
       </c>
       <c r="B108" t="n">
         <v>99118</v>
@@ -14062,7 +14053,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -14081,10 +14072,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>524047</v>
+        <v>524033</v>
       </c>
       <c r="R108" t="n">
-        <v>6713301</v>
+        <v>6713299</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14116,7 +14107,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -14126,7 +14117,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -14152,13 +14143,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126934164</t>
+          <t>https://artportalen.se/Sighting/126933692</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126934577</v>
+        <v>126934164</v>
       </c>
       <c r="B109" t="n">
         <v>99118</v>
@@ -14188,7 +14179,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -14207,10 +14198,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>524036</v>
+        <v>524047</v>
       </c>
       <c r="R109" t="n">
-        <v>6713293</v>
+        <v>6713301</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14242,7 +14233,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14252,7 +14243,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14278,13 +14269,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126934577</t>
+          <t>https://artportalen.se/Sighting/126934164</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126934586</v>
+        <v>126934577</v>
       </c>
       <c r="B110" t="n">
         <v>99118</v>
@@ -14314,7 +14305,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -14327,18 +14318,16 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>524034</v>
+        <v>524036</v>
       </c>
       <c r="R110" t="n">
-        <v>6713294</v>
+        <v>6713293</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14370,7 +14359,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14380,7 +14369,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14389,7 +14378,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -14407,13 +14395,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126934586</t>
+          <t>https://artportalen.se/Sighting/126934577</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126934603</v>
+        <v>126934586</v>
       </c>
       <c r="B111" t="n">
         <v>99118</v>
@@ -14443,7 +14431,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -14456,6 +14444,8 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
@@ -14465,7 +14455,7 @@
         <v>524034</v>
       </c>
       <c r="R111" t="n">
-        <v>6713296</v>
+        <v>6713294</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14497,7 +14487,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -14507,7 +14497,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14516,6 +14506,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -14533,13 +14524,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126934603</t>
+          <t>https://artportalen.se/Sighting/126934586</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126935325</v>
+        <v>126934603</v>
       </c>
       <c r="B112" t="n">
         <v>99118</v>
@@ -14588,10 +14579,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>524091</v>
+        <v>524034</v>
       </c>
       <c r="R112" t="n">
-        <v>6713327</v>
+        <v>6713296</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14623,7 +14614,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14633,7 +14624,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14659,13 +14650,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126935325</t>
+          <t>https://artportalen.se/Sighting/126934603</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126936299</v>
+        <v>126935325</v>
       </c>
       <c r="B113" t="n">
         <v>99118</v>
@@ -14695,7 +14686,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -14714,10 +14705,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>524172</v>
+        <v>524091</v>
       </c>
       <c r="R113" t="n">
-        <v>6713431</v>
+        <v>6713327</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14749,7 +14740,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14759,7 +14750,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14785,13 +14776,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126936299</t>
+          <t>https://artportalen.se/Sighting/126935325</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126936539</v>
+        <v>126936299</v>
       </c>
       <c r="B114" t="n">
         <v>99118</v>
@@ -14840,10 +14831,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>524155</v>
+        <v>524172</v>
       </c>
       <c r="R114" t="n">
-        <v>6713596</v>
+        <v>6713431</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14875,7 +14866,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14885,7 +14876,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14911,13 +14902,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126936539</t>
+          <t>https://artportalen.se/Sighting/126936299</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126961591</v>
+        <v>126936539</v>
       </c>
       <c r="B115" t="n">
         <v>99118</v>
@@ -14947,12 +14938,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -14962,14 +14953,14 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524075</v>
+        <v>524155</v>
       </c>
       <c r="R115" t="n">
-        <v>6714105</v>
+        <v>6713596</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -14996,27 +14987,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>8 I blom över ytan, rikligt med bladrosetter också.</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15042,13 +15028,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126961591</t>
+          <t>https://artportalen.se/Sighting/126936539</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126962144</v>
+        <v>126961591</v>
       </c>
       <c r="B116" t="n">
         <v>99118</v>
@@ -15078,12 +15064,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -15097,10 +15083,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524099</v>
+        <v>524075</v>
       </c>
       <c r="R116" t="n">
-        <v>6713924</v>
+        <v>6714105</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15132,7 +15118,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -15142,7 +15128,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>8 I blom över ytan, rikligt med bladrosetter också.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15168,13 +15159,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126962144</t>
+          <t>https://artportalen.se/Sighting/126961591</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126962269</v>
+        <v>126962144</v>
       </c>
       <c r="B117" t="n">
         <v>99118</v>
@@ -15223,10 +15214,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524049</v>
+        <v>524099</v>
       </c>
       <c r="R117" t="n">
-        <v>6713929</v>
+        <v>6713924</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15258,7 +15249,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15268,7 +15259,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15294,13 +15285,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126962269</t>
+          <t>https://artportalen.se/Sighting/126962144</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126962421</v>
+        <v>126962269</v>
       </c>
       <c r="B118" t="n">
         <v>99118</v>
@@ -15330,7 +15321,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -15345,14 +15336,14 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524038</v>
+        <v>524049</v>
       </c>
       <c r="R118" t="n">
-        <v>6713919</v>
+        <v>6713929</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15384,7 +15375,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15394,7 +15385,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15420,13 +15411,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126962421</t>
+          <t>https://artportalen.se/Sighting/126962269</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126962844</v>
+        <v>126962421</v>
       </c>
       <c r="B119" t="n">
         <v>99118</v>
@@ -15456,7 +15447,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -15471,14 +15462,14 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524143</v>
+        <v>524038</v>
       </c>
       <c r="R119" t="n">
-        <v>6713665</v>
+        <v>6713919</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15510,7 +15501,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15520,7 +15511,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15546,13 +15537,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126962844</t>
+          <t>https://artportalen.se/Sighting/126962421</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126963368</v>
+        <v>126962844</v>
       </c>
       <c r="B120" t="n">
         <v>99118</v>
@@ -15597,14 +15588,14 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524091</v>
+        <v>524143</v>
       </c>
       <c r="R120" t="n">
-        <v>6713407</v>
+        <v>6713665</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15636,7 +15627,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15646,7 +15637,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15672,13 +15663,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126963368</t>
+          <t>https://artportalen.se/Sighting/126962844</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126963427</v>
+        <v>126963368</v>
       </c>
       <c r="B121" t="n">
         <v>99118</v>
@@ -15727,10 +15718,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524088</v>
+        <v>524091</v>
       </c>
       <c r="R121" t="n">
-        <v>6713405</v>
+        <v>6713407</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15762,7 +15753,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15772,7 +15763,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15798,13 +15789,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126963427</t>
+          <t>https://artportalen.se/Sighting/126963368</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126963583</v>
+        <v>126963427</v>
       </c>
       <c r="B122" t="n">
         <v>99118</v>
@@ -15834,7 +15825,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -15847,21 +15838,16 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524077</v>
+        <v>524088</v>
       </c>
       <c r="R122" t="n">
-        <v>6713430</v>
+        <v>6713405</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15893,7 +15879,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15903,12 +15889,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Över yta på ca 5 kv/m</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15934,13 +15915,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126963583</t>
+          <t>https://artportalen.se/Sighting/126963427</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127727170</v>
+        <v>126963583</v>
       </c>
       <c r="B123" t="n">
         <v>99118</v>
@@ -15970,7 +15951,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -15978,16 +15959,26 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>524154</v>
+        <v>524077</v>
       </c>
       <c r="R123" t="n">
-        <v>6713653</v>
+        <v>6713430</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16014,22 +16005,27 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Över yta på ca 5 kv/m</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16055,13 +16051,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127727170</t>
+          <t>https://artportalen.se/Sighting/126963583</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127727173</v>
+        <v>127727170</v>
       </c>
       <c r="B124" t="n">
         <v>99118</v>
@@ -16091,7 +16087,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -16108,7 +16104,7 @@
         <v>524154</v>
       </c>
       <c r="R124" t="n">
-        <v>6713656</v>
+        <v>6713653</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16176,13 +16172,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127727173</t>
+          <t>https://artportalen.se/Sighting/127727170</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129064197</v>
+        <v>127727173</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -16217,24 +16213,19 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>524099</v>
+        <v>524154</v>
       </c>
       <c r="R125" t="n">
-        <v>6714137</v>
+        <v>6713656</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16246,7 +16237,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -16256,27 +16247,27 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>Aspeboda</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -16302,13 +16293,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129064197</t>
+          <t>https://artportalen.se/Sighting/127727173</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129064260</v>
+        <v>129064197</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -16336,7 +16327,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K126" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -16348,10 +16348,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>524107</v>
+        <v>524099</v>
       </c>
       <c r="R126" t="n">
-        <v>6714128</v>
+        <v>6714137</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -16383,7 +16383,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -16393,7 +16393,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -16419,13 +16419,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129064260</t>
+          <t>https://artportalen.se/Sighting/129064197</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129114973</v>
+        <v>129064260</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -16453,34 +16453,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>524137</v>
+        <v>524107</v>
       </c>
       <c r="R127" t="n">
-        <v>6713729</v>
+        <v>6714128</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -16489,7 +16480,7 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
@@ -16499,27 +16490,27 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Aspeboda</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -16545,13 +16536,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129114973</t>
+          <t>https://artportalen.se/Sighting/129064260</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129115572</v>
+        <v>129114973</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -16581,32 +16572,32 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524075</v>
+        <v>524137</v>
       </c>
       <c r="R128" t="n">
-        <v>6713417</v>
+        <v>6713729</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -16635,7 +16626,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -16645,7 +16636,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16671,44 +16662,53 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129115572</t>
+          <t>https://artportalen.se/Sighting/129114973</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>123569808</v>
+        <v>129115572</v>
       </c>
       <c r="B129" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -16717,10 +16717,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524077</v>
+        <v>524075</v>
       </c>
       <c r="R129" t="n">
-        <v>6713436</v>
+        <v>6713417</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -16747,22 +16747,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16788,16 +16788,16 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123569808</t>
+          <t>https://artportalen.se/Sighting/129115572</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>123569630</v>
+        <v>123569808</v>
       </c>
       <c r="B130" t="n">
-        <v>101326</v>
+        <v>97983</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16805,35 +16805,24 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="N130" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -16845,10 +16834,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524047</v>
+        <v>524077</v>
       </c>
       <c r="R130" t="n">
-        <v>6713427</v>
+        <v>6713436</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16880,7 +16869,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -16890,12 +16879,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16904,7 +16888,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -16922,13 +16905,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123569630</t>
+          <t>https://artportalen.se/Sighting/123569808</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>123762639</v>
+        <v>123569630</v>
       </c>
       <c r="B131" t="n">
         <v>101326</v>
@@ -16958,14 +16941,10 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -16979,14 +16958,14 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>524016</v>
+        <v>524047</v>
       </c>
       <c r="R131" t="n">
-        <v>6713966</v>
+        <v>6713427</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -17013,27 +16992,27 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>På större yta, ca 35x15m, kanske mer. På avverkningsyta där dom dragit basväg rakt över växtplatsen.</t>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -17060,13 +17039,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123762639</t>
+          <t>https://artportalen.se/Sighting/123569630</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>123768932</v>
+        <v>123762639</v>
       </c>
       <c r="B132" t="n">
         <v>101326</v>
@@ -17096,12 +17075,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -17109,16 +17088,22 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524000</v>
+        <v>524016</v>
       </c>
       <c r="R132" t="n">
-        <v>6713968</v>
+        <v>6713966</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -17145,22 +17130,27 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>På större yta, ca 35x15m, kanske mer. På avverkningsyta där dom dragit basväg rakt över växtplatsen.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -17169,6 +17159,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -17186,13 +17177,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123768932</t>
+          <t>https://artportalen.se/Sighting/123762639</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>123768976</v>
+        <v>123768932</v>
       </c>
       <c r="B133" t="n">
         <v>101326</v>
@@ -17220,7 +17211,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -17232,10 +17232,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524011</v>
+        <v>524000</v>
       </c>
       <c r="R133" t="n">
-        <v>6713981</v>
+        <v>6713968</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -17267,7 +17267,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -17303,13 +17303,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123768976</t>
+          <t>https://artportalen.se/Sighting/123768932</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>123768989</v>
+        <v>123768976</v>
       </c>
       <c r="B134" t="n">
         <v>101326</v>
@@ -17349,10 +17349,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R134" t="n">
-        <v>6713958</v>
+        <v>6713981</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17384,7 +17384,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17420,13 +17420,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123768989</t>
+          <t>https://artportalen.se/Sighting/123768976</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>123768995</v>
+        <v>123768989</v>
       </c>
       <c r="B135" t="n">
         <v>101326</v>
@@ -17466,10 +17466,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R135" t="n">
-        <v>6713982</v>
+        <v>6713958</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17537,13 +17537,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123768995</t>
+          <t>https://artportalen.se/Sighting/123768989</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>123769023</v>
+        <v>123768995</v>
       </c>
       <c r="B136" t="n">
         <v>101326</v>
@@ -17583,10 +17583,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R136" t="n">
-        <v>6713986</v>
+        <v>6713982</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -17654,13 +17654,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123769023</t>
+          <t>https://artportalen.se/Sighting/123768995</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>123769072</v>
+        <v>123769023</v>
       </c>
       <c r="B137" t="n">
         <v>101326</v>
@@ -17688,31 +17688,22 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>524031</v>
+        <v>524017</v>
       </c>
       <c r="R137" t="n">
-        <v>6713998</v>
+        <v>6713986</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -17744,7 +17735,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -17754,7 +17745,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -17780,13 +17771,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123769072</t>
+          <t>https://artportalen.se/Sighting/123769023</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>123769093</v>
+        <v>123769072</v>
       </c>
       <c r="B138" t="n">
         <v>101326</v>
@@ -17816,29 +17807,29 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>524033</v>
+        <v>524031</v>
       </c>
       <c r="R138" t="n">
-        <v>6713983</v>
+        <v>6713998</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17870,7 +17861,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -17880,7 +17871,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -17906,13 +17897,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123769093</t>
+          <t>https://artportalen.se/Sighting/123769072</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>123769126</v>
+        <v>123769093</v>
       </c>
       <c r="B139" t="n">
         <v>101326</v>
@@ -17940,7 +17931,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -17952,10 +17952,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>524017</v>
+        <v>524033</v>
       </c>
       <c r="R139" t="n">
-        <v>6713977</v>
+        <v>6713983</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -17987,7 +17987,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -18023,16 +18023,16 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123769126</t>
+          <t>https://artportalen.se/Sighting/123769093</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130321255</v>
+        <v>123769126</v>
       </c>
       <c r="B140" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -18057,34 +18057,25 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>524148</v>
+        <v>524017</v>
       </c>
       <c r="R140" t="n">
-        <v>6713407</v>
+        <v>6713977</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -18108,22 +18099,22 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -18149,16 +18140,16 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130321255</t>
+          <t>https://artportalen.se/Sighting/123769126</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132755530</v>
+        <v>130321255</v>
       </c>
       <c r="B141" t="n">
-        <v>101403</v>
+        <v>101325</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -18185,29 +18176,29 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>524009</v>
+        <v>524148</v>
       </c>
       <c r="R141" t="n">
-        <v>6714085</v>
+        <v>6713407</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -18219,7 +18210,7 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
@@ -18229,27 +18220,27 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Aspeboda</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -18274,6 +18265,132 @@
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321255</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>132755530</v>
+      </c>
+      <c r="B142" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>524009</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6714085</v>
+      </c>
+      <c r="S142" t="n">
+        <v>5</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132755530</t>
         </is>
@@ -18421,6 +18538,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -4998,7 +4998,7 @@
         <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -4998,7 +4998,7 @@
         <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -5024,11 +5024,7 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Smedsbo, Dlr</t>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -4998,7 +4998,7 @@
         <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -4998,7 +4998,7 @@
         <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -4998,7 +4998,7 @@
         <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 5108-2023 artfynd.xlsx
+++ b/artfynd/A 5108-2023 artfynd.xlsx
@@ -4998,7 +4998,7 @@
         <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
